--- a/PMI-DZT2/ПМИ ЛО/pmi_lodzt/example.xlsx
+++ b/PMI-DZT2/ПМИ ЛО/pmi_lodzt/example.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ  ЛО\pmi_lodzt\lonn1_modes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ЛО\pmi_lodzt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F4953D-C513-4614-90C6-AB791071AFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4B4B97-E06D-4B90-B556-CA0DBD48ABA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SGF_Parameters" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="129">
   <si>
     <t>IA</t>
   </si>
@@ -412,6 +412,9 @@
   </si>
   <si>
     <t>DZT2_SignAssembly_1_OCSign</t>
+  </si>
+  <si>
+    <t>TECH_OCControl</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1196,7 @@
         <v>73</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>75</v>
